--- a/Submission/Table 5.xlsx
+++ b/Submission/Table 5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <t xml:space="preserve">Table 5: Model summary and performance statistics for the random forest regression using the training and test data sets. </t>
   </si>
@@ -159,6 +159,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">§</t>
     </r>
@@ -191,6 +192,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -200,6 +202,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(CI</t>
     </r>
@@ -210,6 +213,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">95%</t>
     </r>
@@ -219,6 +223,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
@@ -291,42 +296,10 @@
     <t xml:space="preserve">&lt;0.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0.31)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0.01)</t>
-    </r>
+    <t xml:space="preserve">&lt;0.01 (0, 0.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;0.01 (0, 0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">Ni</t>
@@ -389,48 +362,13 @@
     <t xml:space="preserve">0.03 (0, 0.42)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(0, 0)</t>
-    </r>
+    <t xml:space="preserve">&lt;0.01 (0, 0)</t>
   </si>
   <si>
     <t xml:space="preserve">x</t>
   </si>
   <si>
     <t xml:space="preserve">0.31 (0.02, 0.67)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0)</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Forest</t>
@@ -556,11 +494,12 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -614,31 +553,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <vertAlign val="superscript"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <vertAlign val="subscript"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
@@ -709,29 +623,33 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -739,15 +657,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -755,43 +665,27 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -802,16 +696,8 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -940,75 +826,78 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="1.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>0.43</v>
       </c>
       <c r="D5" s="9" t="n">
@@ -1023,13 +912,13 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>57.4</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="D6" s="9" t="n">
@@ -1044,13 +933,13 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>34.4</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="D7" s="9" t="n">
@@ -1065,13 +954,13 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="9" t="n">
         <v>1.86</v>
       </c>
       <c r="D8" s="9" t="n">
@@ -1086,13 +975,13 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="10" t="n">
         <v>37.4</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.39</v>
       </c>
       <c r="D9" s="9" t="n">
@@ -1107,34 +996,34 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0.95</v>
       </c>
       <c r="E10" s="9"/>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>65.1</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="9" t="n">
         <v>1.89</v>
       </c>
       <c r="D11" s="9" t="n">
@@ -1149,13 +1038,13 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="10" t="n">
         <v>76.1</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="9" t="n">
         <v>3.75</v>
       </c>
       <c r="D12" s="9" t="n">
@@ -1170,13 +1059,13 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="10" t="n">
         <v>64.4</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="9" t="n">
         <v>441.33</v>
       </c>
       <c r="D13" s="9" t="n">
@@ -1191,13 +1080,13 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="10" t="n">
         <v>41.5</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.03</v>
       </c>
       <c r="D14" s="9" t="n">
@@ -1212,13 +1101,13 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="10" t="n">
         <v>31.8</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="9" t="n">
         <v>0.53</v>
       </c>
       <c r="D15" s="9" t="n">
@@ -1233,13 +1122,13 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="9" t="n">
         <v>0.64</v>
       </c>
       <c r="D16" s="9" t="n">
@@ -1254,13 +1143,13 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="9" t="n">
@@ -1270,18 +1159,18 @@
       <c r="F17" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="13" t="n">
         <v>34.5</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="9" t="n">
@@ -1291,29 +1180,29 @@
       <c r="F18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>41.5</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="7" t="n">
         <v>0.32</v>
       </c>
       <c r="D20" s="9" t="n">
@@ -1321,20 +1210,20 @@
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="9" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="9" t="n">
         <v>0.97</v>
       </c>
       <c r="D21" s="9" t="n">
@@ -1342,20 +1231,20 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="9" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="D22" s="9" t="n">
@@ -1363,20 +1252,20 @@
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="9" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="9" t="n">
         <v>0.55</v>
       </c>
       <c r="D23" s="9" t="n">
@@ -1384,20 +1273,20 @@
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="9" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="9" t="n">
         <v>2.49</v>
       </c>
       <c r="D24" s="9" t="n">
@@ -1405,20 +1294,20 @@
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="10" t="n">
         <v>36.1</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="9" t="n">
@@ -1426,20 +1315,20 @@
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="9" t="n">
         <v>7.78</v>
       </c>
       <c r="D26" s="9" t="n">
@@ -1447,20 +1336,20 @@
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="10" t="n">
         <v>40.1</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="9" t="n">
         <v>44.47</v>
       </c>
       <c r="D27" s="9" t="n">
@@ -1468,87 +1357,87 @@
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="9" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="16" t="s">
+      <c r="C28" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19" t="s">
+      <c r="G28" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="11">
